--- a/data/trans_orig/IP31B_R_2023-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/IP31B_R_2023-Provincia-trans_orig.xlsx
@@ -541,7 +541,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -552,7 +552,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -720,72 +720,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>30734</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>24144</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>36885</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>51,0%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>40,06%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>61,21%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>42</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>33362</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>25481</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>43394</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>46,73%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>35,69%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>60,78%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>51</t>
-        </is>
-      </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>40503</t>
+          <t>24799</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>32869</t>
+          <t>18875</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>48521</t>
+          <t>30578</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>54,29%</t>
+          <t>45,15%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>44,06%</t>
+          <t>34,37%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>65,04%</t>
+          <t>55,68%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>73865</t>
+          <t>55534</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>62051</t>
+          <t>46973</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>86463</t>
+          <t>64190</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>50,59%</t>
+          <t>48,21%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>42,5%</t>
+          <t>40,78%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>59,22%</t>
+          <t>55,73%</t>
         </is>
       </c>
     </row>
@@ -833,72 +833,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>29529</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>23378</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>36119</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>49,0%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>38,79%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>59,94%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>50</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>38038</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>28006</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>45919</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>53,27%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>39,22%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>64,31%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>42</t>
-        </is>
-      </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>34104</t>
+          <t>30123</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>26086</t>
+          <t>24344</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>41738</t>
+          <t>36047</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>45,71%</t>
+          <t>54,85%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>34,96%</t>
+          <t>44,32%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>55,94%</t>
+          <t>65,63%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>72142</t>
+          <t>59652</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>59544</t>
+          <t>50996</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>83956</t>
+          <t>68213</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>49,41%</t>
+          <t>51,79%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>40,78%</t>
+          <t>44,27%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>57,5%</t>
+          <t>59,22%</t>
         </is>
       </c>
     </row>
@@ -946,57 +946,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>93</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>60263</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>60263</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>60263</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>92</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>71400</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>71400</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>71400</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>93</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>74607</t>
+          <t>54922</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>74607</t>
+          <t>54922</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>74607</t>
+          <t>54922</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>146007</t>
+          <t>115186</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>146007</t>
+          <t>115186</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>146007</t>
+          <t>115186</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1063,72 +1063,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>86</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>55968</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>44838</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>65906</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>48,82%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>39,11%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>57,48%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>60</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>66680</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>47411</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>94148</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>54,13%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>38,49%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>76,42%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>86</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>63169</t>
+          <t>41566</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>51862</t>
+          <t>32648</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>76026</t>
+          <t>50156</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>50,12%</t>
+          <t>42,75%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>41,15%</t>
+          <t>33,58%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>60,32%</t>
+          <t>51,58%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1138,32 +1138,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>129849</t>
+          <t>97534</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>108274</t>
+          <t>84308</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>168413</t>
+          <t>112305</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>52,1%</t>
+          <t>46,03%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>43,45%</t>
+          <t>39,79%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>67,58%</t>
+          <t>53,0%</t>
         </is>
       </c>
     </row>
@@ -1176,72 +1176,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>58684</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>48746</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>69814</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>51,18%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>42,52%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>60,89%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>75</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>56510</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>29042</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>75779</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>45,87%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>23,58%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>61,51%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>66</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>62858</t>
+          <t>55665</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>50001</t>
+          <t>47075</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>74165</t>
+          <t>64583</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>49,88%</t>
+          <t>57,25%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>39,68%</t>
+          <t>48,42%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>58,85%</t>
+          <t>66,42%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1251,32 +1251,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>119368</t>
+          <t>114349</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>80804</t>
+          <t>99578</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>140943</t>
+          <t>127575</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>47,9%</t>
+          <t>53,97%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>32,42%</t>
+          <t>47,0%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>56,55%</t>
+          <t>60,21%</t>
         </is>
       </c>
     </row>
@@ -1289,57 +1289,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>152</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>114652</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>114652</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>114652</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>135</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>123190</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>123190</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>123190</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>152</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>126027</t>
+          <t>97231</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>126027</t>
+          <t>97231</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>126027</t>
+          <t>97231</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>249217</t>
+          <t>211883</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>249217</t>
+          <t>211883</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>249217</t>
+          <t>211883</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1406,72 +1406,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>24600</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>18733</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>30243</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>42,93%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>32,69%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>52,78%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>40</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>24548</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>18568</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>30075</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>44,19%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>33,43%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>54,14%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>42</t>
-        </is>
-      </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>28070</t>
+          <t>23824</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>21962</t>
+          <t>18567</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>35265</t>
+          <t>29381</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>43,43%</t>
+          <t>44,03%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>33,98%</t>
+          <t>34,31%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>54,56%</t>
+          <t>54,3%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1481,32 +1481,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>52619</t>
+          <t>48424</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>44142</t>
+          <t>40623</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>61470</t>
+          <t>56620</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>43,78%</t>
+          <t>43,46%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>36,73%</t>
+          <t>36,46%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>51,15%</t>
+          <t>50,82%</t>
         </is>
       </c>
     </row>
@@ -1519,72 +1519,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>32699</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>27056</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>38566</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>57,07%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>47,22%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>67,31%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>51</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>31004</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>25477</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>36984</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>55,81%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>45,86%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>66,57%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>53</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>36563</t>
+          <t>30288</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>29368</t>
+          <t>24731</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>42671</t>
+          <t>35545</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>56,57%</t>
+          <t>55,97%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>45,44%</t>
+          <t>45,7%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>66,02%</t>
+          <t>65,69%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1594,32 +1594,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>67566</t>
+          <t>62987</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>58715</t>
+          <t>54791</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>76043</t>
+          <t>70788</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>56,22%</t>
+          <t>56,54%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>48,85%</t>
+          <t>49,18%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>63,27%</t>
+          <t>63,54%</t>
         </is>
       </c>
     </row>
@@ -1632,57 +1632,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>95</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>57299</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>57299</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>57299</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>91</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>55552</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>55552</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>55552</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>95</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>64633</t>
+          <t>54112</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>64633</t>
+          <t>54112</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>64633</t>
+          <t>54112</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>120185</t>
+          <t>111411</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>120185</t>
+          <t>111411</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>120185</t>
+          <t>111411</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1749,72 +1749,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>14823</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>7886</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>23480</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>22,05%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>11,73%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>34,93%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>29</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>18105</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>12502</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>24751</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>26,39%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>18,23%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>36,08%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>15654</t>
+          <t>17586</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>8522</t>
+          <t>11676</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>24455</t>
+          <t>24577</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>21,88%</t>
+          <t>25,39%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>11,91%</t>
+          <t>16,86%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>34,18%</t>
+          <t>35,48%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,32 +1824,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>33759</t>
+          <t>32409</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>23574</t>
+          <t>23431</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>45850</t>
+          <t>43774</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>24,09%</t>
+          <t>23,74%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>16,82%</t>
+          <t>17,17%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>32,72%</t>
+          <t>32,07%</t>
         </is>
       </c>
     </row>
@@ -1862,72 +1862,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>52400</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>43743</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>59337</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>77,95%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>65,07%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>88,27%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>63</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>50492</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>43846</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>56095</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>73,61%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>63,92%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>81,77%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>44</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>55898</t>
+          <t>51688</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>47097</t>
+          <t>44697</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>63030</t>
+          <t>57598</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>78,12%</t>
+          <t>74,61%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>65,82%</t>
+          <t>64,52%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>88,09%</t>
+          <t>83,14%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,32 +1937,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>106390</t>
+          <t>104087</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>94299</t>
+          <t>92722</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>116575</t>
+          <t>113065</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>75,91%</t>
+          <t>76,26%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>67,28%</t>
+          <t>67,93%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>83,18%</t>
+          <t>82,83%</t>
         </is>
       </c>
     </row>
@@ -1975,57 +1975,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>67223</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>67223</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>67223</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>92</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>68597</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>68597</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>68597</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>71552</t>
+          <t>69274</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>71552</t>
+          <t>69274</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>71552</t>
+          <t>69274</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2050,17 +2050,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>140149</t>
+          <t>136496</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>140149</t>
+          <t>136496</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>140149</t>
+          <t>136496</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2097,7 +2097,7 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>576</t>
+          <t>472</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -2107,12 +2107,12 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>2340</t>
+          <t>2442</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
@@ -2122,7 +2122,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>6,84%</t>
+          <t>6,17%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2132,7 +2132,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>587</t>
+          <t>619</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>3323</t>
+          <t>3515</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
@@ -2157,7 +2157,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>8,16%</t>
+          <t>9,94%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,7 +2167,7 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>1163</t>
+          <t>1090</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
@@ -2177,12 +2177,12 @@
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>3632</t>
+          <t>3587</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
@@ -2192,7 +2192,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,85%</t>
+          <t>4,79%</t>
         </is>
       </c>
     </row>
@@ -2205,74 +2205,74 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>39107</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>37137</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>39579</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>98,81%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>93,83%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>66</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>33624</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>31860</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>34200</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>98,32%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>93,16%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>34751</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>31855</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>35370</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>98,25%</t>
+        </is>
+      </c>
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>90,06%</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>40132</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>37396</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>40719</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>98,56%</t>
-        </is>
-      </c>
-      <c r="O17" s="2" t="inlineStr">
-        <is>
-          <t>91,84%</t>
-        </is>
-      </c>
-      <c r="P17" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q17" s="2" t="inlineStr">
         <is>
           <t>136</t>
@@ -2280,27 +2280,27 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>73756</t>
+          <t>73859</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>71287</t>
+          <t>71362</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>74919</t>
+          <t>74949</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>98,45%</t>
+          <t>98,55%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>95,15%</t>
+          <t>95,21%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -2318,57 +2318,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>39579</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>39579</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>39579</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>67</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>34200</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>34200</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>34200</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>71</t>
-        </is>
-      </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>40719</t>
+          <t>35370</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>40719</t>
+          <t>35370</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>40719</t>
+          <t>35370</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2393,17 +2393,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>74919</t>
+          <t>74949</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>74919</t>
+          <t>74949</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>74919</t>
+          <t>74949</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2435,72 +2435,72 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>31183</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>26028</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>36127</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>66,05%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>55,13%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>76,53%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>41</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>24798</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>19886</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>29797</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>55,99%</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>44,9%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>67,28%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>36073</t>
+          <t>23993</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>30096</t>
+          <t>18951</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>41410</t>
+          <t>28932</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>67,07%</t>
+          <t>54,18%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>55,96%</t>
+          <t>42,79%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>77,0%</t>
+          <t>65,33%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2510,32 +2510,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>60870</t>
+          <t>55177</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>53675</t>
+          <t>48029</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>68983</t>
+          <t>62731</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>62,07%</t>
+          <t>60,31%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>54,73%</t>
+          <t>52,49%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>70,34%</t>
+          <t>68,56%</t>
         </is>
       </c>
     </row>
@@ -2548,72 +2548,72 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>16026</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>11082</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>21181</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>33,95%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>23,47%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>44,87%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>33</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>19492</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>14493</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>24404</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>44,01%</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>32,72%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>55,1%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>17709</t>
+          <t>20293</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>12372</t>
+          <t>15354</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>23686</t>
+          <t>25335</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>32,93%</t>
+          <t>45,82%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>23,0%</t>
+          <t>34,67%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>44,04%</t>
+          <t>57,21%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2623,32 +2623,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>37202</t>
+          <t>36318</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>29089</t>
+          <t>28764</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>44397</t>
+          <t>43466</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>37,93%</t>
+          <t>39,69%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>29,66%</t>
+          <t>31,44%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>45,27%</t>
+          <t>47,51%</t>
         </is>
       </c>
     </row>
@@ -2661,57 +2661,57 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>87</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>47209</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>47209</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>47209</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>74</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>44290</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>44290</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>44290</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>87</t>
-        </is>
-      </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>53782</t>
+          <t>44286</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>53782</t>
+          <t>44286</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>53782</t>
+          <t>44286</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2736,17 +2736,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>98072</t>
+          <t>91495</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>98072</t>
+          <t>91495</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>98072</t>
+          <t>91495</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2778,72 +2778,72 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>48232</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>37932</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>60945</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>34,54%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>27,17%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>43,65%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
           <t>51</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>34291</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>26118</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>43797</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>27,81%</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>21,18%</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>35,52%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>61</t>
-        </is>
-      </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>54827</t>
+          <t>32674</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>43246</t>
+          <t>25356</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>69703</t>
+          <t>41064</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>35,58%</t>
+          <t>26,9%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>28,07%</t>
+          <t>20,87%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>45,24%</t>
+          <t>33,8%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2853,32 +2853,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>89118</t>
+          <t>80906</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>74790</t>
+          <t>68082</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>107383</t>
+          <t>96668</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>32,13%</t>
+          <t>30,99%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>26,96%</t>
+          <t>26,07%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>38,71%</t>
+          <t>37,02%</t>
         </is>
       </c>
     </row>
@@ -2891,72 +2891,72 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>114</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>91396</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>78683</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>101696</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>65,46%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>56,35%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>72,83%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>122</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>89014</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>79508</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>97187</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>72,19%</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>64,48%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>78,82%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>114</t>
-        </is>
-      </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>99247</t>
+          <t>88808</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>84371</t>
+          <t>80418</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>110828</t>
+          <t>96126</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>64,42%</t>
+          <t>73,1%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>54,76%</t>
+          <t>66,2%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>71,93%</t>
+          <t>79,13%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2966,32 +2966,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>188260</t>
+          <t>180204</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>169995</t>
+          <t>164442</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>202588</t>
+          <t>193028</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>67,87%</t>
+          <t>69,01%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>61,29%</t>
+          <t>62,98%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>73,04%</t>
+          <t>73,93%</t>
         </is>
       </c>
     </row>
@@ -3004,57 +3004,57 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>175</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>139628</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>139628</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>139628</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
           <t>173</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>123305</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>123305</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>123305</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>175</t>
-        </is>
-      </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>154074</t>
+          <t>121482</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>154074</t>
+          <t>121482</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>154074</t>
+          <t>121482</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3079,17 +3079,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>277378</t>
+          <t>261110</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>277378</t>
+          <t>261110</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>277378</t>
+          <t>261110</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3121,72 +3121,72 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>19846</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>13672</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>27687</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>12,63%</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>8,7%</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>17,62%</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
           <t>25</t>
         </is>
       </c>
-      <c r="D25" s="2" t="inlineStr">
-        <is>
-          <t>17366</t>
-        </is>
-      </c>
-      <c r="E25" s="2" t="inlineStr">
-        <is>
-          <t>11427</t>
-        </is>
-      </c>
-      <c r="F25" s="2" t="inlineStr">
-        <is>
-          <t>24607</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="inlineStr">
-        <is>
-          <t>13,5%</t>
-        </is>
-      </c>
-      <c r="H25" s="2" t="inlineStr">
-        <is>
-          <t>8,88%</t>
-        </is>
-      </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>19,12%</t>
-        </is>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>20266</t>
+          <t>18742</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>13741</t>
+          <t>12330</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>28117</t>
+          <t>28200</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>13,15%</t>
+          <t>13,59%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>8,91%</t>
+          <t>8,94%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>18,24%</t>
+          <t>20,45%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3196,32 +3196,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>37632</t>
+          <t>38589</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>28184</t>
+          <t>29275</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>48393</t>
+          <t>50609</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>13,31%</t>
+          <t>13,08%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>9,97%</t>
+          <t>9,92%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>17,11%</t>
+          <t>17,15%</t>
         </is>
       </c>
     </row>
@@ -3234,72 +3234,72 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>172</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>137290</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>129449</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>143464</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>87,37%</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>82,38%</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>91,3%</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
           <t>159</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
-        <is>
-          <t>111299</t>
-        </is>
-      </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>104058</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>117238</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>86,5%</t>
-        </is>
-      </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>80,88%</t>
-        </is>
-      </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>91,12%</t>
-        </is>
-      </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>172</t>
-        </is>
-      </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>133893</t>
+          <t>119158</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>126042</t>
+          <t>109700</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>140418</t>
+          <t>125570</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>86,85%</t>
+          <t>86,41%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>81,76%</t>
+          <t>79,55%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>91,09%</t>
+          <t>91,06%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3309,32 +3309,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>245191</t>
+          <t>256447</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>234430</t>
+          <t>244427</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>254639</t>
+          <t>265761</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>86,69%</t>
+          <t>86,92%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>82,89%</t>
+          <t>82,85%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>90,03%</t>
+          <t>90,08%</t>
         </is>
       </c>
     </row>
@@ -3347,57 +3347,57 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
+          <t>202</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>157136</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>157136</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>157136</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
           <t>184</t>
         </is>
       </c>
-      <c r="D27" s="2" t="inlineStr">
-        <is>
-          <t>128665</t>
-        </is>
-      </c>
-      <c r="E27" s="2" t="inlineStr">
-        <is>
-          <t>128665</t>
-        </is>
-      </c>
-      <c r="F27" s="2" t="inlineStr">
-        <is>
-          <t>128665</t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J27" s="2" t="inlineStr">
-        <is>
-          <t>202</t>
-        </is>
-      </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>154159</t>
+          <t>137900</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>154159</t>
+          <t>137900</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>154159</t>
+          <t>137900</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3422,17 +3422,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>282823</t>
+          <t>295036</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>282823</t>
+          <t>295036</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>282823</t>
+          <t>295036</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3464,72 +3464,72 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>347</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>225858</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>204522</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>250878</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>33,07%</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>29,95%</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>36,73%</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
           <t>289</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
-        <is>
-          <t>219727</t>
-        </is>
-      </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>192703</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>282508</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>33,85%</t>
-        </is>
-      </c>
-      <c r="H28" s="2" t="inlineStr">
-        <is>
-          <t>29,68%</t>
-        </is>
-      </c>
-      <c r="I28" s="2" t="inlineStr">
-        <is>
-          <t>43,52%</t>
-        </is>
-      </c>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>347</t>
-        </is>
-      </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>259149</t>
+          <t>183803</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>233608</t>
+          <t>165303</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>288414</t>
+          <t>203868</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>35,04%</t>
+          <t>29,91%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>31,59%</t>
+          <t>26,9%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>39,0%</t>
+          <t>33,17%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3539,32 +3539,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>478876</t>
+          <t>409662</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>440688</t>
+          <t>380431</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>541957</t>
+          <t>441822</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>34,48%</t>
+          <t>31,57%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>31,73%</t>
+          <t>29,32%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>39,02%</t>
+          <t>34,05%</t>
         </is>
       </c>
     </row>
@@ -3577,72 +3577,72 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
+          <t>588</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>457130</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>432110</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>478466</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>66,93%</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>63,27%</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>70,05%</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
           <t>619</t>
         </is>
       </c>
-      <c r="D29" s="2" t="inlineStr">
-        <is>
-          <t>429472</t>
-        </is>
-      </c>
-      <c r="E29" s="2" t="inlineStr">
-        <is>
-          <t>366691</t>
-        </is>
-      </c>
-      <c r="F29" s="2" t="inlineStr">
-        <is>
-          <t>456496</t>
-        </is>
-      </c>
-      <c r="G29" s="2" t="inlineStr">
-        <is>
-          <t>66,15%</t>
-        </is>
-      </c>
-      <c r="H29" s="2" t="inlineStr">
-        <is>
-          <t>56,48%</t>
-        </is>
-      </c>
-      <c r="I29" s="2" t="inlineStr">
-        <is>
-          <t>70,32%</t>
-        </is>
-      </c>
-      <c r="J29" s="2" t="inlineStr">
-        <is>
-          <t>588</t>
-        </is>
-      </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>480404</t>
+          <t>430773</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>451139</t>
+          <t>410708</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>505945</t>
+          <t>449273</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>64,96%</t>
+          <t>70,09%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>61,0%</t>
+          <t>66,83%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>68,41%</t>
+          <t>73,1%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3652,32 +3652,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>909876</t>
+          <t>887903</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>846795</t>
+          <t>855743</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>948064</t>
+          <t>917134</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>65,52%</t>
+          <t>68,43%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>60,98%</t>
+          <t>65,95%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>68,27%</t>
+          <t>70,68%</t>
         </is>
       </c>
     </row>
@@ -3690,57 +3690,57 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
+          <t>935</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>682988</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>682988</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>682988</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
           <t>908</t>
         </is>
       </c>
-      <c r="D30" s="2" t="inlineStr">
-        <is>
-          <t>649199</t>
-        </is>
-      </c>
-      <c r="E30" s="2" t="inlineStr">
-        <is>
-          <t>649199</t>
-        </is>
-      </c>
-      <c r="F30" s="2" t="inlineStr">
-        <is>
-          <t>649199</t>
-        </is>
-      </c>
-      <c r="G30" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H30" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I30" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J30" s="2" t="inlineStr">
-        <is>
-          <t>935</t>
-        </is>
-      </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>739553</t>
+          <t>614576</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>739553</t>
+          <t>614576</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>739553</t>
+          <t>614576</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3765,17 +3765,17 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>1388752</t>
+          <t>1297565</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>1388752</t>
+          <t>1297565</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>1388752</t>
+          <t>1297565</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
